--- a/analysis/data/annotation/[Archived] Labeling SDG 10 - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 10 - Benchmarking Dataset.xlsx
@@ -33,7 +33,7 @@
     <comment authorId="0" ref="C96">
       <text>
         <t xml:space="preserve">Is this already captured by rule 1?
-	-Steve Borchardt
+	-Deleted user
 yes but under 1. we dont make an explicit comment about policy
 	-Meike Morren</t>
       </text>
@@ -50120,7 +50120,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="3" hidden="1">
+    <row r="3">
       <c r="A3" s="23" t="s">
         <v>102</v>
       </c>
@@ -50196,7 +50196,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="5" hidden="1">
+    <row r="5">
       <c r="A5" s="23" t="s">
         <v>272</v>
       </c>
@@ -50231,7 +50231,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" hidden="1">
+    <row r="6">
       <c r="A6" s="23" t="s">
         <v>90</v>
       </c>
@@ -50266,7 +50266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" hidden="1">
+    <row r="7">
       <c r="A7" s="23" t="s">
         <v>78</v>
       </c>
@@ -50342,7 +50342,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="9" hidden="1">
+    <row r="9">
       <c r="A9" s="23" t="s">
         <v>243</v>
       </c>
@@ -50380,7 +50380,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="10" hidden="1">
+    <row r="10">
       <c r="A10" s="23" t="s">
         <v>211</v>
       </c>
@@ -50418,7 +50418,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="11" hidden="1">
+    <row r="11">
       <c r="A11" s="23" t="s">
         <v>142</v>
       </c>
@@ -50456,7 +50456,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="12" hidden="1">
+    <row r="12">
       <c r="A12" s="23" t="s">
         <v>221</v>
       </c>
@@ -50535,7 +50535,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="14" hidden="1">
+    <row r="14">
       <c r="A14" s="23" t="s">
         <v>93</v>
       </c>
@@ -50570,7 +50570,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" hidden="1">
+    <row r="15">
       <c r="A15" s="23" t="s">
         <v>310</v>
       </c>
@@ -50605,7 +50605,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" hidden="1">
+    <row r="16">
       <c r="A16" s="23" t="s">
         <v>303</v>
       </c>
@@ -50640,7 +50640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" hidden="1">
+    <row r="17">
       <c r="A17" s="23" t="s">
         <v>99</v>
       </c>
@@ -50675,7 +50675,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" hidden="1">
+    <row r="18">
       <c r="A18" s="23" t="s">
         <v>68</v>
       </c>
@@ -50710,7 +50710,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="A19" s="23" t="s">
         <v>178</v>
       </c>
@@ -50748,7 +50748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" hidden="1">
+    <row r="20">
       <c r="A20" s="23" t="s">
         <v>306</v>
       </c>
@@ -50786,7 +50786,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="21" hidden="1">
+    <row r="21">
       <c r="A21" s="23" t="s">
         <v>122</v>
       </c>
@@ -50824,7 +50824,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="22" hidden="1">
+    <row r="22">
       <c r="A22" s="23" t="s">
         <v>144</v>
       </c>
@@ -50859,7 +50859,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" hidden="1">
+    <row r="23">
       <c r="A23" s="23" t="s">
         <v>265</v>
       </c>
@@ -50894,7 +50894,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" hidden="1">
+    <row r="24">
       <c r="A24" s="23" t="s">
         <v>128</v>
       </c>
@@ -50929,7 +50929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" hidden="1">
+    <row r="25">
       <c r="A25" s="23" t="s">
         <v>301</v>
       </c>
@@ -50967,7 +50967,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="26" hidden="1">
+    <row r="26">
       <c r="A26" s="23" t="s">
         <v>111</v>
       </c>
@@ -51002,7 +51002,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" hidden="1">
+    <row r="27">
       <c r="A27" s="23" t="s">
         <v>96</v>
       </c>
@@ -51081,7 +51081,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="29" hidden="1">
+    <row r="29">
       <c r="A29" s="23" t="s">
         <v>213</v>
       </c>
@@ -51119,7 +51119,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="30" hidden="1">
+    <row r="30">
       <c r="A30" s="23" t="s">
         <v>175</v>
       </c>
@@ -51154,7 +51154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" hidden="1">
+    <row r="31">
       <c r="A31" s="23" t="s">
         <v>198</v>
       </c>
@@ -51315,7 +51315,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="35" hidden="1">
+    <row r="35">
       <c r="A35" s="23" t="s">
         <v>114</v>
       </c>
@@ -51350,7 +51350,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" hidden="1">
+    <row r="36">
       <c r="A36" s="23" t="s">
         <v>165</v>
       </c>
@@ -51388,7 +51388,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="37" hidden="1">
+    <row r="37">
       <c r="A37" s="23" t="s">
         <v>238</v>
       </c>
@@ -51423,7 +51423,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" hidden="1">
+    <row r="38">
       <c r="A38" s="23" t="s">
         <v>283</v>
       </c>
@@ -51461,7 +51461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" hidden="1">
+    <row r="39">
       <c r="A39" s="23" t="s">
         <v>230</v>
       </c>
@@ -51499,7 +51499,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="40" hidden="1">
+    <row r="40">
       <c r="A40" s="23" t="s">
         <v>208</v>
       </c>
@@ -51537,7 +51537,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="41" hidden="1">
+    <row r="41">
       <c r="A41" s="23" t="s">
         <v>280</v>
       </c>
@@ -51575,7 +51575,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="42" hidden="1">
+    <row r="42">
       <c r="A42" s="23" t="s">
         <v>228</v>
       </c>
@@ -51610,7 +51610,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" hidden="1">
+    <row r="43">
       <c r="A43" s="23" t="s">
         <v>234</v>
       </c>
@@ -51731,7 +51731,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="46" hidden="1">
+    <row r="46">
       <c r="A46" s="23" t="s">
         <v>125</v>
       </c>
@@ -51769,7 +51769,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="47" hidden="1">
+    <row r="47">
       <c r="A47" s="23" t="s">
         <v>147</v>
       </c>
@@ -51804,7 +51804,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" hidden="1">
+    <row r="48">
       <c r="A48" s="23" t="s">
         <v>83</v>
       </c>
@@ -51842,7 +51842,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" hidden="1">
+    <row r="49">
       <c r="A49" s="23" t="s">
         <v>75</v>
       </c>
@@ -51880,7 +51880,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="50" hidden="1">
+    <row r="50">
       <c r="A50" s="23" t="s">
         <v>119</v>
       </c>
@@ -51915,7 +51915,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" hidden="1">
+    <row r="51">
       <c r="A51" s="23" t="s">
         <v>116</v>
       </c>
@@ -51950,7 +51950,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" hidden="1">
+    <row r="52">
       <c r="A52" s="23" t="s">
         <v>170</v>
       </c>
@@ -51985,7 +51985,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" hidden="1">
+    <row r="53">
       <c r="A53" s="23" t="s">
         <v>225</v>
       </c>
@@ -52023,7 +52023,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="54" hidden="1">
+    <row r="54">
       <c r="A54" s="23" t="s">
         <v>162</v>
       </c>
@@ -52061,7 +52061,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="55" hidden="1">
+    <row r="55">
       <c r="A55" s="23" t="s">
         <v>269</v>
       </c>
@@ -52099,7 +52099,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="56" hidden="1">
+    <row r="56">
       <c r="A56" s="23" t="s">
         <v>105</v>
       </c>
@@ -52134,7 +52134,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" hidden="1">
+    <row r="57">
       <c r="A57" s="23" t="s">
         <v>134</v>
       </c>
@@ -52169,7 +52169,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" hidden="1">
+    <row r="58">
       <c r="A58" s="23" t="s">
         <v>131</v>
       </c>
@@ -52207,7 +52207,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="59" hidden="1">
+    <row r="59">
       <c r="A59" s="23" t="s">
         <v>314</v>
       </c>
@@ -52242,7 +52242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" hidden="1">
+    <row r="60">
       <c r="A60" s="23" t="s">
         <v>277</v>
       </c>
@@ -52277,7 +52277,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" hidden="1">
+    <row r="61">
       <c r="A61" s="23" t="s">
         <v>137</v>
       </c>
@@ -52315,7 +52315,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="62" hidden="1">
+    <row r="62">
       <c r="A62" s="23" t="s">
         <v>294</v>
       </c>
@@ -52394,7 +52394,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="64" hidden="1">
+    <row r="64">
       <c r="A64" s="23" t="s">
         <v>73</v>
       </c>
@@ -52432,7 +52432,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="65" hidden="1">
+    <row r="65">
       <c r="A65" s="23" t="s">
         <v>85</v>
       </c>
@@ -52467,7 +52467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" hidden="1">
+    <row r="66">
       <c r="A66" s="23" t="s">
         <v>87</v>
       </c>
@@ -52505,7 +52505,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="67" hidden="1">
+    <row r="67">
       <c r="A67" s="23" t="s">
         <v>64</v>
       </c>
@@ -52543,7 +52543,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="68" hidden="1">
+    <row r="68">
       <c r="A68" s="23" t="s">
         <v>296</v>
       </c>
@@ -52581,7 +52581,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="69" hidden="1">
+    <row r="69">
       <c r="A69" s="23" t="s">
         <v>157</v>
       </c>
@@ -52619,7 +52619,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="70" hidden="1">
+    <row r="70">
       <c r="A70" s="23" t="s">
         <v>232</v>
       </c>
@@ -52654,7 +52654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" hidden="1">
+    <row r="71">
       <c r="A71" s="23" t="s">
         <v>291</v>
       </c>
@@ -52689,7 +52689,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" hidden="1">
+    <row r="72">
       <c r="A72" s="23" t="s">
         <v>251</v>
       </c>
@@ -52724,7 +52724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" hidden="1">
+    <row r="73">
       <c r="A73" s="23" t="s">
         <v>167</v>
       </c>
@@ -52762,7 +52762,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="74" hidden="1">
+    <row r="74">
       <c r="A74" s="23" t="s">
         <v>200</v>
       </c>
@@ -52797,7 +52797,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" hidden="1">
+    <row r="75">
       <c r="A75" s="23" t="s">
         <v>153</v>
       </c>
@@ -52835,7 +52835,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="76" hidden="1">
+    <row r="76">
       <c r="A76" s="23" t="s">
         <v>70</v>
       </c>
@@ -52870,7 +52870,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" hidden="1">
+    <row r="77">
       <c r="A77" s="23" t="s">
         <v>287</v>
       </c>
@@ -52993,7 +52993,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="80" hidden="1">
+    <row r="80">
       <c r="A80" s="23" t="s">
         <v>218</v>
       </c>
@@ -53028,7 +53028,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" hidden="1">
+    <row r="81">
       <c r="A81" s="23" t="s">
         <v>173</v>
       </c>
@@ -53066,7 +53066,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="82" hidden="1">
+    <row r="82">
       <c r="A82" s="23" t="s">
         <v>247</v>
       </c>
@@ -53104,7 +53104,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="83" hidden="1">
+    <row r="83">
       <c r="A83" s="23" t="s">
         <v>215</v>
       </c>
@@ -53139,7 +53139,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" hidden="1">
+    <row r="84">
       <c r="A84" s="23" t="s">
         <v>308</v>
       </c>
@@ -53177,7 +53177,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="85" hidden="1">
+    <row r="85">
       <c r="A85" s="23" t="s">
         <v>249</v>
       </c>
@@ -53212,7 +53212,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" hidden="1">
+    <row r="86">
       <c r="A86" s="23" t="s">
         <v>140</v>
       </c>
@@ -53247,7 +53247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" hidden="1">
+    <row r="87">
       <c r="A87" s="23" t="s">
         <v>205</v>
       </c>
@@ -53285,7 +53285,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" hidden="1">
+    <row r="88">
       <c r="A88" s="23" t="s">
         <v>275</v>
       </c>
@@ -53361,7 +53361,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="90" hidden="1">
+    <row r="90">
       <c r="A90" s="23" t="s">
         <v>81</v>
       </c>
@@ -53399,7 +53399,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="91" hidden="1">
+    <row r="91">
       <c r="A91" s="23" t="s">
         <v>261</v>
       </c>
@@ -53434,7 +53434,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" hidden="1">
+    <row r="92">
       <c r="A92" s="23" t="s">
         <v>190</v>
       </c>
@@ -53510,7 +53510,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="94" hidden="1">
+    <row r="94">
       <c r="A94" s="23" t="s">
         <v>150</v>
       </c>
@@ -53548,7 +53548,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="95" hidden="1">
+    <row r="95">
       <c r="A95" s="23" t="s">
         <v>159</v>
       </c>
@@ -53584,7 +53584,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="96" hidden="1">
+    <row r="96">
       <c r="A96" s="23" t="s">
         <v>245</v>
       </c>
@@ -53622,7 +53622,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="97" hidden="1">
+    <row r="97">
       <c r="A97" s="23" t="s">
         <v>236</v>
       </c>
@@ -53658,7 +53658,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" hidden="1">
+    <row r="98">
       <c r="A98" s="23" t="s">
         <v>259</v>
       </c>
@@ -53694,7 +53694,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" hidden="1">
+    <row r="99">
       <c r="A99" s="23" t="s">
         <v>312</v>
       </c>
@@ -53730,7 +53730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" hidden="1">
+    <row r="100">
       <c r="A100" s="23" t="s">
         <v>181</v>
       </c>
@@ -53766,7 +53766,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" hidden="1">
+    <row r="101">
       <c r="A101" s="23" t="s">
         <v>108</v>
       </c>
@@ -62793,22 +62793,7 @@
       <c r="J1000" s="42"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$L$101">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="financial market regulation falls under target 10.5"/>
-        <filter val="ensuring equal opportunities falls under target 10.3"/>
-        <filter val="irregular migration falls under target 10.7"/>
-        <filter val="gender equality is part of SDG 10"/>
-        <filter val="inequality between different population segments"/>
-        <filter val="richer countries have greater ability than poorer countries / unequal opportunity"/>
-        <filter val="ensuring economic inclusion of women falls under target 10.2"/>
-        <filter val="no explicit connection to inequality"/>
-        <filter val="not specific to orderly, safe, regular or responsible migration"/>
-        <filter val="social protection policies fall under target 10.4"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="$A$1:$L$101"/>
   <conditionalFormatting sqref="D2:I126">
     <cfRule type="beginsWith" dxfId="0" priority="1" operator="beginsWith" text="SDG">
       <formula>LEFT((D2),LEN("SDG"))=("SDG")</formula>
